--- a/kuuube's_wacom_nib_compatibility_mastersheet.xlsx
+++ b/kuuube's_wacom_nib_compatibility_mastersheet.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Wacom Nib Compatibility Masters" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Kuuubes Info" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Wacom Nib Compatibility Masters" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Kuuubes Info" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -430,6 +430,10 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/kuuube's_wacom_nib_compatibility_mastersheet.xlsx
+++ b/kuuube's_wacom_nib_compatibility_mastersheet.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="91">
   <si>
     <t>Kuuube's Wacom Nib Compatibility Mastersheet</t>
   </si>
@@ -29,37 +29,58 @@
     <t>ACK-24911Z</t>
   </si>
   <si>
+    <t>Standard (POM)</t>
+  </si>
+  <si>
+    <t>CP-923, CP-913</t>
+  </si>
+  <si>
+    <t>ACK-24918Z</t>
+  </si>
+  <si>
+    <t>Elastomer</t>
+  </si>
+  <si>
+    <t>ACK-24919Z</t>
+  </si>
+  <si>
+    <t>Felt</t>
+  </si>
+  <si>
+    <t>ACK-24501Z</t>
+  </si>
+  <si>
     <t>Standard</t>
   </si>
   <si>
-    <t>CP-923, CP-913</t>
-  </si>
-  <si>
-    <t>ACK-24918Z</t>
-  </si>
-  <si>
-    <t>Elastomer</t>
-  </si>
-  <si>
-    <t>ACK-24919Z</t>
-  </si>
-  <si>
-    <t>Felt</t>
-  </si>
-  <si>
-    <t>ACK-24501Z</t>
+    <t>ACK-256011Z</t>
+  </si>
+  <si>
+    <t>Standard (Carbon POM)</t>
+  </si>
+  <si>
+    <t>ACP-500, ACP-501E, ACP-700</t>
+  </si>
+  <si>
+    <t>ACK-25611Z</t>
+  </si>
+  <si>
+    <t>ACK-25619Z</t>
   </si>
   <si>
     <t>ACK-24801Z</t>
   </si>
   <si>
+    <t xml:space="preserve">ACP-500, ACP-501E, KP-504E, KP-301E, KP-505                </t>
+  </si>
+  <si>
+    <t>ACK-24819Z</t>
+  </si>
+  <si>
     <t xml:space="preserve">ACP-500, ACP-501E, KP-504E, KP-301E, KP-505		</t>
   </si>
   <si>
-    <t>ACK-24819Z</t>
-  </si>
-  <si>
-    <t>ACK253010Z</t>
+    <t>ACK-253010Z</t>
   </si>
   <si>
     <t>Rubber</t>
@@ -638,6 +659,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="13.63"/>
+    <col customWidth="1" min="2" max="2" width="19.13"/>
     <col customWidth="1" min="3" max="6" width="88.5"/>
     <col customWidth="1" min="7" max="7" width="50.88"/>
   </cols>
@@ -701,7 +723,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>6</v>
@@ -709,65 +731,76 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>21</v>
@@ -775,436 +808,468 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2"/>
-    </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="A19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>3</v>
+      <c r="A25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>25</v>
+      <c r="A28" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
+        <v>32</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="s">
-        <v>62</v>
+      <c r="A50" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="C52" s="2" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="s">
-        <v>65</v>
+      <c r="A53" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="s">
-        <v>69</v>
+      <c r="A57" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="56">
+  <mergeCells count="59">
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="C3:G3"/>
@@ -1247,16 +1312,9 @@
     <mergeCell ref="C40:G40"/>
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C43:G43"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
     <mergeCell ref="C47:G47"/>
     <mergeCell ref="C48:G48"/>
     <mergeCell ref="C49:G49"/>
@@ -1278,17 +1336,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
@@ -1299,57 +1357,57 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="K15" s="11"/>
     </row>
